--- a/data/trans_dic/P36$cafe-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P36$cafe-Edad-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que desayuna, al menos, café, leche, té, chololate, yogurt,...</t>
+          <t>Población que desayuna, al menos, café, leche, té, chololate, yogurt,... (tasa de respuesta: 99,85%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>85,75; 91,11</t>
+          <t>85,5; 91,13</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>79,74; 86,77</t>
+          <t>79,6; 86,83</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>80,49; 88,02</t>
+          <t>80,88; 88,01</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>80,82; 86,86</t>
+          <t>80,81; 87,38</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>81,93; 88,74</t>
+          <t>81,77; 88,62</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>81,87; 88,9</t>
+          <t>82,23; 89,03</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>84,11; 88,68</t>
+          <t>84,08; 88,47</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>81,86; 86,85</t>
+          <t>81,83; 86,78</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>82,71; 87,76</t>
+          <t>82,21; 87,4</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>86,85; 91,31</t>
+          <t>86,65; 91,73</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>85,03; 90,17</t>
+          <t>85,17; 90,25</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>83,95; 89,5</t>
+          <t>84,23; 89,39</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>86,1; 91,01</t>
+          <t>85,8; 91,11</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>88,15; 93,27</t>
+          <t>88,31; 93,11</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>88,21; 93,09</t>
+          <t>88,38; 93,37</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>87,17; 90,53</t>
+          <t>87,17; 90,49</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>87,55; 91,21</t>
+          <t>87,44; 91,15</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>87,09; 90,72</t>
+          <t>86,9; 90,83</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>90,57; 94,57</t>
+          <t>90,44; 94,55</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>90,29; 94,48</t>
+          <t>90,08; 94,49</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>89,83; 94,17</t>
+          <t>89,95; 94,27</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>90,63; 94,54</t>
+          <t>90,57; 94,72</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>93,33; 96,54</t>
+          <t>93,16; 96,51</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>91,23; 95,14</t>
+          <t>91,03; 95,11</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>91,2; 94,17</t>
+          <t>91,21; 94,26</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>92,49; 95,05</t>
+          <t>92,46; 95,16</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>91,2; 94,05</t>
+          <t>91,25; 94,18</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>89,78; 94,64</t>
+          <t>89,85; 94,94</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>91,84; 96,16</t>
+          <t>91,94; 96,11</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>89,28; 93,79</t>
+          <t>89,4; 93,74</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>90,12; 94,86</t>
+          <t>90,22; 94,79</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>94,19; 97,53</t>
+          <t>94,07; 97,49</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,84; 96,39</t>
+          <t>93,01; 96,49</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>90,68; 94,13</t>
+          <t>90,68; 94,2</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>93,74; 96,33</t>
+          <t>93,8; 96,39</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>91,79; 94,66</t>
+          <t>91,9; 94,67</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>89,71; 94,82</t>
+          <t>89,3; 94,79</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>91,48; 96,72</t>
+          <t>91,67; 96,44</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>89,28; 94,59</t>
+          <t>88,88; 94,4</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>90,37; 95,28</t>
+          <t>90,33; 95,41</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>92,74; 97,03</t>
+          <t>92,51; 96,98</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>93,96; 97,78</t>
+          <t>94,02; 97,68</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>90,94; 94,49</t>
+          <t>90,51; 94,43</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>93,21; 96,36</t>
+          <t>93,11; 96,33</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>92,56; 95,66</t>
+          <t>92,4; 95,76</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>92,05; 97,21</t>
+          <t>92,14; 97,23</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>92,09; 97,24</t>
+          <t>92,63; 97,4</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>91,66; 96,52</t>
+          <t>91,82; 96,71</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>91,93; 96,79</t>
+          <t>92,31; 96,77</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>93,31; 97,45</t>
+          <t>93,34; 97,51</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>93,12; 97,32</t>
+          <t>93,22; 97,35</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>93,13; 96,44</t>
+          <t>92,95; 96,5</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>93,81; 97,01</t>
+          <t>93,39; 96,83</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>93,42; 96,53</t>
+          <t>93,56; 96,48</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>89,36; 96,45</t>
+          <t>89,17; 96,23</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>92,41; 98,26</t>
+          <t>92,49; 98,29</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>92,46; 97,65</t>
+          <t>92,95; 97,65</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>94,61; 98,67</t>
+          <t>94,51; 98,67</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>93,39; 97,77</t>
+          <t>93,24; 97,73</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,0; 99,4</t>
+          <t>96,14; 99,37</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>93,59; 97,21</t>
+          <t>93,7; 97,32</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>94,16; 97,45</t>
+          <t>94,06; 97,43</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>95,71; 98,42</t>
+          <t>95,59; 98,35</t>
         </is>
       </c>
     </row>
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>90,48; 92,43</t>
+          <t>90,33; 92,38</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>90,44; 92,4</t>
+          <t>90,49; 92,37</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>89,7; 91,82</t>
+          <t>89,74; 91,83</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>90,66; 92,53</t>
+          <t>90,53; 92,5</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>92,69; 94,4</t>
+          <t>92,72; 94,27</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>92,74; 94,38</t>
+          <t>92,74; 94,4</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>90,89; 92,16</t>
+          <t>90,79; 92,19</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>91,92; 93,2</t>
+          <t>91,89; 93,21</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>91,51; 92,85</t>
+          <t>91,62; 92,88</t>
         </is>
       </c>
     </row>
@@ -1543,7 +1543,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que desayuna, al menos, café, leche, té, chololate, yogurt,...</t>
+          <t>Población que desayuna, al menos, café, leche, té, chololate, yogurt,... (tasa de respuesta: 99,85%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1750,47 +1750,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>422891; 449339</t>
+          <t>421669; 449430</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>362154; 394059</t>
+          <t>361495; 394320</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>337610; 369217</t>
+          <t>339258; 369163</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>377812; 406072</t>
+          <t>377774; 408476</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>350848; 380008</t>
+          <t>350187; 379497</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>323223; 351002</t>
+          <t>324650; 351510</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>807962; 851922</t>
+          <t>807731; 849900</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>722293; 766343</t>
+          <t>722030; 765755</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>673446; 714610</t>
+          <t>669440; 711671</t>
         </is>
       </c>
     </row>
@@ -1913,47 +1913,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>638794; 671566</t>
+          <t>637331; 674632</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>583461; 618714</t>
+          <t>584377; 619277</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>495732; 528520</t>
+          <t>497354; 527821</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>536757; 567387</t>
+          <t>534896; 568013</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>536907; 568086</t>
+          <t>537866; 567102</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>497122; 524610</t>
+          <t>498042; 526193</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1184553; 1230215</t>
+          <t>1184573; 1229637</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1134019; 1181359</t>
+          <t>1132585; 1180676</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1005046; 1046923</t>
+          <t>1002860; 1048227</t>
         </is>
       </c>
     </row>
@@ -2076,47 +2076,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>574940; 600278</t>
+          <t>574061; 600151</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>613110; 641573</t>
+          <t>611680; 641639</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>601079; 630114</t>
+          <t>601862; 630745</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>625094; 652069</t>
+          <t>624685; 653332</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>661601; 684363</t>
+          <t>660392; 684137</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>603351; 629217</t>
+          <t>602072; 629045</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1207950; 1247285</t>
+          <t>1208101; 1248440</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1283731; 1319208</t>
+          <t>1283233; 1320775</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1213367; 1251380</t>
+          <t>1214103; 1253070</t>
         </is>
       </c>
     </row>
@@ -2239,47 +2239,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>464367; 489481</t>
+          <t>464730; 491065</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>563501; 590041</t>
+          <t>564092; 589685</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>574844; 603886</t>
+          <t>575604; 603570</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>462953; 487286</t>
+          <t>463454; 486912</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>580411; 600994</t>
+          <t>579679; 600721</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>601598; 624597</t>
+          <t>602663; 625225</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>934845; 970414</t>
+          <t>934875; 971144</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1152810; 1184625</t>
+          <t>1153580; 1185403</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1185796; 1222781</t>
+          <t>1187188; 1222982</t>
         </is>
       </c>
     </row>
@@ -2402,47 +2402,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>346918; 366676</t>
+          <t>345351; 366580</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>392846; 415327</t>
+          <t>393676; 414159</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>426672; 452067</t>
+          <t>424778; 451134</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>365087; 384924</t>
+          <t>364901; 385424</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>414347; 433496</t>
+          <t>413287; 433284</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>466827; 485807</t>
+          <t>467129; 485315</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>719062; 747164</t>
+          <t>715628; 746691</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>816700; 844286</t>
+          <t>815835; 844053</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>902247; 932480</t>
+          <t>900670; 933410</t>
         </is>
       </c>
     </row>
@@ -2565,47 +2565,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>269324; 284429</t>
+          <t>269580; 284471</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>285270; 301228</t>
+          <t>286950; 301741</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>306445; 322697</t>
+          <t>306995; 323314</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>315256; 331938</t>
+          <t>316548; 331858</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>330301; 344978</t>
+          <t>330424; 345198</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>351776; 367625</t>
+          <t>352139; 367748</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>591860; 612905</t>
+          <t>590689; 613250</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>622714; 643938</t>
+          <t>619929; 642732</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>665266; 687371</t>
+          <t>666203; 686999</t>
         </is>
       </c>
     </row>
@@ -2728,47 +2728,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>187552; 202436</t>
+          <t>187163; 201975</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>229884; 244434</t>
+          <t>230087; 244502</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>235966; 249214</t>
+          <t>237216; 249212</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>315924; 329474</t>
+          <t>315577; 329484</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>363273; 380295</t>
+          <t>362680; 380160</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>383029; 396595</t>
+          <t>383563; 396457</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>508939; 528632</t>
+          <t>509537; 529223</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>600524; 621499</t>
+          <t>599859; 621361</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>626118; 643835</t>
+          <t>625314; 643409</t>
         </is>
       </c>
     </row>
@@ -2891,47 +2891,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>2958647; 3022335</t>
+          <t>2953472; 3020686</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3093794; 3160962</t>
+          <t>3095519; 3160006</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3041234; 3112948</t>
+          <t>3042692; 3113510</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3060053; 3122923</t>
+          <t>3055452; 3122071</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>3292647; 3353261</t>
+          <t>3293620; 3348714</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>3284294; 3342354</t>
+          <t>3284043; 3342862</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>6039320; 6124212</t>
+          <t>6033195; 6125749</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>6409528; 6498596</t>
+          <t>6407334; 6499895</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>6343469; 6435749</t>
+          <t>6350672; 6437806</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P36$cafe-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P36$cafe-Edad-trans_dic.xlsx
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>85,5; 91,13</t>
+          <t>85,54; 91,37</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>79,6; 86,83</t>
+          <t>79,32; 86,44</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>80,88; 88,01</t>
+          <t>80,69; 87,95</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>80,81; 87,38</t>
+          <t>80,64; 87,3</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>81,77; 88,62</t>
+          <t>81,66; 88,63</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>82,23; 89,03</t>
+          <t>82,26; 89,29</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>84,08; 88,47</t>
+          <t>84,52; 88,73</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>81,83; 86,78</t>
+          <t>82,13; 86,97</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>82,21; 87,4</t>
+          <t>82,68; 87,61</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>86,65; 91,73</t>
+          <t>86,85; 91,38</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>85,17; 90,25</t>
+          <t>85,07; 90,23</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>84,23; 89,39</t>
+          <t>84,22; 89,82</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>85,8; 91,11</t>
+          <t>85,9; 91,14</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>88,31; 93,11</t>
+          <t>88,58; 93,52</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>88,38; 93,37</t>
+          <t>88,2; 93,05</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>87,17; 90,49</t>
+          <t>87,35; 90,58</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>87,44; 91,15</t>
+          <t>87,38; 91,06</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>86,9; 90,83</t>
+          <t>87,05; 90,73</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>90,44; 94,55</t>
+          <t>90,34; 94,44</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>90,08; 94,49</t>
+          <t>90,15; 94,49</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>89,95; 94,27</t>
+          <t>89,78; 94,03</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>90,57; 94,72</t>
+          <t>90,71; 94,75</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>93,16; 96,51</t>
+          <t>93,15; 96,61</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>91,03; 95,11</t>
+          <t>91,22; 95,23</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>91,21; 94,26</t>
+          <t>91,14; 94,06</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>92,46; 95,16</t>
+          <t>92,38; 94,99</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>91,25; 94,18</t>
+          <t>91,09; 94,16</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>89,85; 94,94</t>
+          <t>89,62; 94,72</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>91,94; 96,11</t>
+          <t>92,23; 96,17</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>89,4; 93,74</t>
+          <t>89,26; 93,84</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>90,22; 94,79</t>
+          <t>90,28; 94,78</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>94,07; 97,49</t>
+          <t>93,92; 97,57</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,01; 96,49</t>
+          <t>92,87; 96,38</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>90,68; 94,2</t>
+          <t>90,88; 94,23</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>93,8; 96,39</t>
+          <t>93,81; 96,51</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>91,9; 94,67</t>
+          <t>91,67; 94,58</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>89,3; 94,79</t>
+          <t>89,52; 94,95</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>91,67; 96,44</t>
+          <t>91,4; 96,58</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>88,88; 94,4</t>
+          <t>88,95; 94,44</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>90,33; 95,41</t>
+          <t>90,56; 95,55</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>92,51; 96,98</t>
+          <t>92,82; 97,08</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>94,02; 97,68</t>
+          <t>93,67; 97,64</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>90,51; 94,43</t>
+          <t>90,94; 94,62</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>93,11; 96,33</t>
+          <t>93,06; 96,27</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>92,4; 95,76</t>
+          <t>92,12; 95,64</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>92,14; 97,23</t>
+          <t>91,97; 97,03</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>92,63; 97,4</t>
+          <t>92,29; 97,44</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>91,82; 96,71</t>
+          <t>91,84; 96,76</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>92,31; 96,77</t>
+          <t>92,19; 96,67</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>93,34; 97,51</t>
+          <t>93,47; 97,51</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>93,22; 97,35</t>
+          <t>93,07; 97,36</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>92,95; 96,5</t>
+          <t>93,16; 96,51</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>93,39; 96,83</t>
+          <t>93,66; 96,9</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>93,56; 96,48</t>
+          <t>93,2; 96,46</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>89,17; 96,23</t>
+          <t>89,24; 95,91</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>92,49; 98,29</t>
+          <t>92,5; 98,26</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>92,95; 97,65</t>
+          <t>92,79; 97,57</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>94,51; 98,67</t>
+          <t>94,81; 98,69</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>93,24; 97,73</t>
+          <t>93,47; 97,68</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,14; 99,37</t>
+          <t>96,28; 99,4</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>93,7; 97,32</t>
+          <t>93,48; 97,17</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>94,06; 97,43</t>
+          <t>93,96; 97,38</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>95,59; 98,35</t>
+          <t>95,55; 98,3</t>
         </is>
       </c>
     </row>
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>90,33; 92,38</t>
+          <t>90,49; 92,46</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>90,49; 92,37</t>
+          <t>90,41; 92,44</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>89,74; 91,83</t>
+          <t>89,73; 91,74</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>90,53; 92,5</t>
+          <t>90,57; 92,49</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>92,72; 94,27</t>
+          <t>92,69; 94,42</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>92,74; 94,4</t>
+          <t>92,65; 94,37</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>90,79; 92,19</t>
+          <t>90,89; 92,19</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>91,89; 93,21</t>
+          <t>91,89; 93,17</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>91,62; 92,88</t>
+          <t>91,64; 92,88</t>
         </is>
       </c>
     </row>
@@ -1750,47 +1750,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>421669; 449430</t>
+          <t>421858; 450625</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>361495; 394320</t>
+          <t>360241; 392578</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>339258; 369163</t>
+          <t>338445; 368910</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>377774; 408476</t>
+          <t>376986; 408105</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>350187; 379497</t>
+          <t>349720; 379565</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>324650; 351510</t>
+          <t>324753; 352519</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>807731; 849900</t>
+          <t>811933; 852420</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>722030; 765755</t>
+          <t>724694; 767427</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>669440; 711671</t>
+          <t>673213; 713351</t>
         </is>
       </c>
     </row>
@@ -1913,47 +1913,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>637331; 674632</t>
+          <t>638800; 672095</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>584377; 619277</t>
+          <t>583691; 619124</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>497354; 527821</t>
+          <t>497308; 530381</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>534896; 568013</t>
+          <t>535531; 568184</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>537866; 567102</t>
+          <t>539550; 569655</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>498042; 526193</t>
+          <t>497070; 524399</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1184573; 1229637</t>
+          <t>1187013; 1230911</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1132585; 1180676</t>
+          <t>1131812; 1179442</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1002860; 1048227</t>
+          <t>1004576; 1047037</t>
         </is>
       </c>
     </row>
@@ -2076,47 +2076,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>574061; 600151</t>
+          <t>573450; 599463</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>611680; 641639</t>
+          <t>612125; 641580</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>601862; 630745</t>
+          <t>600729; 629123</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>624685; 653332</t>
+          <t>625672; 653523</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>660392; 684137</t>
+          <t>660319; 684848</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>602072; 629045</t>
+          <t>603336; 629806</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1208101; 1248440</t>
+          <t>1207196; 1245902</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1283233; 1320775</t>
+          <t>1282209; 1318446</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1214103; 1253070</t>
+          <t>1211902; 1252735</t>
         </is>
       </c>
     </row>
@@ -2239,47 +2239,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>464730; 491065</t>
+          <t>463532; 489881</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>564092; 589685</t>
+          <t>565887; 590103</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>575604; 603570</t>
+          <t>574730; 604225</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>463454; 486912</t>
+          <t>463735; 486865</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>579679; 600721</t>
+          <t>578728; 601220</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>602663; 625225</t>
+          <t>601793; 624494</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>934875; 971144</t>
+          <t>936846; 971452</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1153580; 1185403</t>
+          <t>1153700; 1186886</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1187188; 1222982</t>
+          <t>1184155; 1221862</t>
         </is>
       </c>
     </row>
@@ -2402,47 +2402,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>345351; 366580</t>
+          <t>346192; 367177</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>393676; 414159</t>
+          <t>392500; 414728</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>424778; 451134</t>
+          <t>425093; 451345</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>364901; 385424</t>
+          <t>365867; 386017</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>413287; 433284</t>
+          <t>414669; 433732</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>467129; 485315</t>
+          <t>465416; 485116</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>715628; 746691</t>
+          <t>719040; 748143</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>815835; 844053</t>
+          <t>815388; 843493</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>900670; 933410</t>
+          <t>898000; 932298</t>
         </is>
       </c>
     </row>
@@ -2565,47 +2565,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>269580; 284471</t>
+          <t>269099; 283894</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>286950; 301741</t>
+          <t>285899; 301844</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>306995; 323314</t>
+          <t>307051; 323505</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>316548; 331858</t>
+          <t>316136; 331515</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>330424; 345198</t>
+          <t>330886; 345176</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>352139; 367748</t>
+          <t>351572; 367784</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>590689; 613250</t>
+          <t>592079; 613306</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>619929; 642732</t>
+          <t>621672; 643218</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>666203; 686999</t>
+          <t>663657; 686876</t>
         </is>
       </c>
     </row>
@@ -2728,47 +2728,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>187163; 201975</t>
+          <t>187294; 201297</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>230087; 244502</t>
+          <t>230106; 244449</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>237216; 249212</t>
+          <t>236802; 249023</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>315577; 329484</t>
+          <t>316594; 329530</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>362680; 380160</t>
+          <t>363597; 379963</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>383563; 396457</t>
+          <t>384146; 396563</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>509537; 529223</t>
+          <t>508322; 528396</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>599859; 621361</t>
+          <t>599230; 621050</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>625314; 643409</t>
+          <t>625082; 643037</t>
         </is>
       </c>
     </row>
@@ -2891,47 +2891,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>2953472; 3020686</t>
+          <t>2958997; 3023394</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3095519; 3160006</t>
+          <t>3092777; 3162417</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3042692; 3113510</t>
+          <t>3042248; 3110167</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3055452; 3122071</t>
+          <t>3056925; 3121659</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>3293620; 3348714</t>
+          <t>3292393; 3353797</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>3284043; 3342862</t>
+          <t>3280832; 3341743</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>6033195; 6125749</t>
+          <t>6039299; 6126045</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>6407334; 6499895</t>
+          <t>6407585; 6497022</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>6350672; 6437806</t>
+          <t>6352029; 6437817</t>
         </is>
       </c>
     </row>
